--- a/data/trans_camb/IP16A05-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-0.4986402788309807</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.130953925745287</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.920419005297659</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.380839215680402</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.204838489567083</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.306050808507725</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-2.631540254896144</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.026980368615469</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.839357993109748</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.663990824003633</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-3.168278010162516</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-3.420970400461309</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>1.56588914821337</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.101839802100033</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.033724653441503</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.68166583891957</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.5470593530043474</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.084300089961382</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.2119920500442981</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.4808140284745371</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.3870980866670912</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.2783352054474808</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3325427972731976</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3604780167656639</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.7438092346275652</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.6861664036446622</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.7970243469679007</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6567987640273998</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7792837777887156</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>1.563092886654388</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2.867821311099531</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.4766513432324555</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.207497219464634</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2693492283958277</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.4718484644705074</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-2.510253228058213</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.049591805862383</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.100413432173134</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.969127848763513</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.802758144313003</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-3.012465436800231</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-5.746241096504402</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.20871103324045</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.688580582812531</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.455369267979849</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-3.680905352378618</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-5.006841659804877</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>0.3158329757904274</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-1.574262257693253</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.108578508056085</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-0.1186825577487982</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.05479722327543576</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-1.536593337460613</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.524714497016405</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.8464801494064884</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.3824000840662819</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6842834092068332</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4708202071250369</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.7867553422990069</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.8265645592378895</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.8247235959366208</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.9324159608763012</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.75667467694296</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.9266901232811987</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.1909034021558003</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.2806014177863912</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.8208360319076391</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.288831622546701</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.04235638828838677</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.419947676772046</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>2.36983415519656</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.7802761014703792</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.272543937419246</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.6421622789394563</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.5451606510625582</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.06161591090148473</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>0.7785340601668918</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.1424409425618067</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.644077707095883</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.065460032928565</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.111083979776021</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.244978374064755</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>5.163099359485204</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.612945072493396</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.991075134406842</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.550778303275145</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.188994023593862</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.252089839428107</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>8.450555334625022</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>2.782374605118316</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.5897041334004302</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.297581670124823</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.4527265762678505</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.05116869739531712</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -913,13 +1026,18 @@
       </c>
       <c r="C20" s="6" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.8556231418012331</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6076594947897688</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6929397553746465</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -930,13 +1048,18 @@
       </c>
       <c r="C21" s="6" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="n">
+        <v>3.558731317165926</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>2.977933023415603</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>3.607892849404201</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2.430769035374158</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1072,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.800488182308836</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.4406602136574279</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-2.684712254892862</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.227511733358547</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.662624674175928</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-1.235060485683826</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1098,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-5.11239819917775</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.28416872533479</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-7.773680786329574</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-7.529602413073193</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-5.173325968441158</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-4.790948153615727</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1124,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2.814248406308105</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.357559029968984</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.91389816289174</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.452674669622025</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.161830267854372</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1.229372354109334</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1150,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.2676973590469319</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1473645433376788</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.5115833911107641</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.4244618782566916</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.4139751871867162</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.3075164248968543</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1176,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.8487985521868555</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.8619426085423768</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.8335680939021753</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.7427101774191153</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1202,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>3.177077838190116</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>4.700201034946865</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1.109183759077676</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.9992711483834119</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.6511779264571858</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.625060506958606</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1232,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.5455338457876112</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-1.417646458456979</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-1.570272490357041</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1.742203698950015</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.045955333413387</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-1.589691710478586</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1258,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.898940541978436</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-2.71199861218573</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.145538626852256</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-3.349755605696337</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.012659467265047</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-2.522522248399778</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1284,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.7667915916338158</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-0.1956112006568219</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-0.2067521113917318</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-0.3968854076997689</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.07053360639600433</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-0.5098032199818109</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1310,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.2005894282361632</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.521259853515334</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.4228614730900283</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.4691611341884936</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.3263438292327297</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.4959925759010143</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1336,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.5510933702503386</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.7763237739714046</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.6728269737160476</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.7105628990783057</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.537879347071115</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.6649802168006494</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1362,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.3813896052720795</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.07170539898539893</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.03337657175775609</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.08899310955115419</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.03196922718190235</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.1835265525894792</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1390,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
